--- a/tests/evals/timesheets/39-xlsx-expenses-line/input.xlsx
+++ b/tests/evals/timesheets/39-xlsx-expenses-line/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,159 +447,61 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-02  8.00</t>
+          <t>Week starts on | Total Hours | State | Time Sheet Approver</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-03  8.00</t>
+          <t>01/31/2026 | 40.00 | Approved | Grace Okafor</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-04  8.00</t>
+          <t>02/07/2026 | 40.00 | Approved | Grace Okafor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-05  8.00</t>
+          <t>02/14/2026 | 40.00 | Approved | Grace Okafor</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-06  8.00</t>
+          <t>02/21/2026 | 40.00 | Approved | Grace Okafor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-09  8.00</t>
+          <t>02/28/2026 | 40.00 | Approved | Grace Okafor</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-10  8.00</t>
+          <t>Total: 160.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-11  8.00</t>
+          <t>State: Approved</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-02-12  8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-02-13  8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-02-16  8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-02-17  8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-02-18  8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-02-19  8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-02-20  8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-02-23  8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-02-24  8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-02-25  8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-02-26  8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-02-27  8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Total: 160.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Approved by Grace Okafor on 2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
         <is>
           <t>Expenses: 214.50 travel</t>
         </is>

--- a/tests/evals/timesheets/39-xlsx-expenses-line/input.xlsx
+++ b/tests/evals/timesheets/39-xlsx-expenses-line/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,89 +517,82 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-16  8.00</t>
+          <t>2026-02-17  8.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-17  8.00</t>
+          <t>2026-02-18  8.00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-18  8.00</t>
+          <t>2026-02-19  8.00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-19  8.00</t>
+          <t>2026-02-20  8.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-20  8.00</t>
+          <t>2026-02-23  8.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-23  8.00</t>
+          <t>2026-02-24  8.00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-24  8.00</t>
+          <t>2026-02-25  8.00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-25  8.00</t>
+          <t>2026-02-26  8.00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-26  8.00</t>
+          <t>2026-02-27  8.00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-27  8.00</t>
+          <t>Total: 152.00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Total: 160.00</t>
+          <t>Approved by Grace Okafor on 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
-        <is>
-          <t>Approved by Grace Okafor on 2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
         <is>
           <t>Expenses: 214.50 travel</t>
         </is>
